--- a/reports/attendance_report_2026-06.xlsx
+++ b/reports/attendance_report_2026-06.xlsx
@@ -436,11 +436,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -455,7 +455,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>员工001</t>
+          <t>技术员工01</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -565,13 +565,13 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -580,10 +580,10 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -592,17 +592,17 @@
         <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>54</v>
+        <v>225</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>员工002</t>
+          <t>技术员工02</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -626,7 +626,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -641,10 +641,10 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10.23</v>
+        <v>27</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -656,14 +656,14 @@
         <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>167.25</v>
+        <v>225</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>167.25</v>
+        <v>225</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>员工003</t>
+          <t>技术员工03</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -687,14 +687,14 @@
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10.28</v>
+        <v>26.92</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.28</v>
+        <v>2.92</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -714,17 +714,17 @@
         <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>员工004</t>
+          <t>技术员工04</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -748,13 +748,13 @@
         <v>3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10.07</v>
+        <v>26.84</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.07</v>
+        <v>2.84</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -775,17 +775,17 @@
         <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>155.25</v>
+        <v>213</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>155.25</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>员工005</t>
+          <t>技术员工05</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -809,13 +809,13 @@
         <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -824,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>26.75</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -839,14 +839,14 @@
         <v>75</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>140.25</v>
+        <v>206.25</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>65.25</v>
+        <v>131.25</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>员工006</t>
+          <t>技术员工06</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9.85</v>
+        <v>27</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -900,14 +900,14 @@
         <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>138.75</v>
+        <v>225</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>138.75</v>
+        <v>225</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>员工007</t>
+          <t>技术员工07</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>26.92</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -961,14 +961,14 @@
         <v>0</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>133.5</v>
+        <v>219</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>133.5</v>
+        <v>219</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>员工008</t>
+          <t>技术员工08</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -992,13 +992,13 @@
         <v>3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9.75</v>
+        <v>26.95</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -1019,17 +1019,17 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>131.25</v>
+        <v>221.25</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>56.25</v>
+        <v>221.25</v>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1041,22 +1041,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>员工009</t>
+          <t>市场员工01</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>技术研发部</t>
+          <t>市场营销部</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>26.84</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1.88</v>
+        <v>2.84</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -1080,17 +1080,17 @@
         <v>0</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1102,25 +1102,25 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>员工010</t>
+          <t>市场员工02</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>技术研发部</t>
+          <t>市场营销部</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9.43</v>
+        <v>27</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1141,17 +1141,17 @@
         <v>0</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>107.25</v>
+        <v>225</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>32.25</v>
+        <v>225</v>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>员工011</t>
+          <t>市场员工03</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1175,11 +1175,11 @@
         <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
@@ -1190,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>10.03</v>
+        <v>26.87</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2.03</v>
+        <v>2.87</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1202,17 +1202,17 @@
         <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>152.25</v>
+        <v>215.25</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>152.25</v>
+        <v>140.25</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>员工012</t>
+          <t>市场员工04</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9.9</v>
+        <v>26.95</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.9</v>
+        <v>2.95</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1266,14 +1266,14 @@
         <v>0</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>142.5</v>
+        <v>221.25</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>142.5</v>
+        <v>221.25</v>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>员工013</t>
+          <t>市场员工05</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1297,13 +1297,13 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9.27</v>
+        <v>27</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.27</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1324,17 +1324,17 @@
         <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>95.25</v>
+        <v>225</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>20.25</v>
+        <v>225</v>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>员工014</t>
+          <t>市场员工06</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1358,11 +1358,11 @@
         <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
       </c>
@@ -1373,10 +1373,10 @@
         <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>10.07</v>
+        <v>26.67</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2.07</v>
+        <v>2.67</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1385,17 +1385,17 @@
         <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>155.25</v>
+        <v>200.25</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>155.25</v>
+        <v>125.25</v>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>员工015</t>
+          <t>市场员工07</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -1434,10 +1434,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>9.85</v>
+        <v>27</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1449,14 +1449,14 @@
         <v>0</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>138.75</v>
+        <v>225</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>138.75</v>
+        <v>225</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>员工016</t>
+          <t>市场员工08</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
         <v>3</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
@@ -1495,10 +1495,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>27</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1510,14 +1510,14 @@
         <v>0</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>146.25</v>
+        <v>225</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>146.25</v>
+        <v>225</v>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1529,19 +1529,19 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>员工017</t>
+          <t>人力员工01</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>市场营销部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
@@ -1556,10 +1556,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9.93</v>
+        <v>26.95</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.93</v>
+        <v>2.95</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1571,14 +1571,14 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>144.75</v>
+        <v>221.25</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>144.75</v>
+        <v>221.25</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1590,25 +1590,25 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>员工018</t>
+          <t>人力员工02</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>市场营销部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9.92</v>
+        <v>26.67</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.92</v>
+        <v>2.67</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1632,14 +1632,14 @@
         <v>75</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>144</v>
+        <v>200.25</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>69</v>
+        <v>125.25</v>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>员工019</t>
+          <t>人力员工03</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>市场营销部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
@@ -1678,10 +1678,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9.58</v>
+        <v>26.87</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1.58</v>
+        <v>2.87</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1693,14 +1693,14 @@
         <v>75</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>118.5</v>
+        <v>215.25</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>43.5</v>
+        <v>140.25</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1712,19 +1712,19 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>员工020</t>
+          <t>人力员工04</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>市场营销部</t>
+          <t>人力资源部</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10.22</v>
+        <v>18</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1754,14 +1754,14 @@
         <v>0</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>166.5</v>
+        <v>150</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>166.5</v>
+        <v>150</v>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>员工021</t>
+          <t>人力员工05</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9.83</v>
+        <v>26.97</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.83</v>
+        <v>2.97</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1815,14 +1815,14 @@
         <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>137.25</v>
+        <v>222.75</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>137.25</v>
+        <v>222.75</v>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>员工022</t>
+          <t>人力员工06</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
         <v>3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
@@ -1861,10 +1861,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9.75</v>
+        <v>17.92</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1876,14 +1876,14 @@
         <v>75</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>131.25</v>
+        <v>144</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>56.25</v>
+        <v>69</v>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>员工023</t>
+          <t>人力员工07</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1907,13 +1907,13 @@
         <v>3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>0</v>
@@ -1922,10 +1922,10 @@
         <v>0</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>26.95</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1.7</v>
+        <v>2.95</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1934,17 +1934,17 @@
         <v>0</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>127.5</v>
+        <v>221.25</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>52.5</v>
+        <v>221.25</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>员工024</t>
+          <t>人力员工08</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1968,7 +1968,7 @@
         <v>3</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9.85</v>
+        <v>26.95</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1998,14 +1998,14 @@
         <v>0</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>138.75</v>
+        <v>221.25</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>138.75</v>
+        <v>221.25</v>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2017,23 +2017,23 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>员工025</t>
+          <t>财务员工01</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>人力资源部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
@@ -2044,10 +2044,10 @@
         <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>10.25</v>
+        <v>26.87</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -2056,17 +2056,17 @@
         <v>0</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>168.75</v>
+        <v>215.25</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>168.75</v>
+        <v>140.25</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2078,25 +2078,25 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>员工026</t>
+          <t>财务员工02</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>人力资源部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>0</v>
@@ -2105,10 +2105,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9.529999999999999</v>
+        <v>27</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -2117,17 +2117,17 @@
         <v>0</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>114.75</v>
+        <v>225</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>39.75</v>
+        <v>225</v>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2139,19 +2139,19 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>员工027</t>
+          <t>财务员工03</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>人力资源部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -2166,10 +2166,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>26.81</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1.97</v>
+        <v>2.81</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -2181,14 +2181,14 @@
         <v>75</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>147.75</v>
+        <v>210.75</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>72.75</v>
+        <v>135.75</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2200,19 +2200,19 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>员工028</t>
+          <t>财务员工04</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>人力资源部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>0</v>
@@ -2227,10 +2227,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9.98</v>
+        <v>27</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1.98</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2242,14 +2242,14 @@
         <v>0</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>148.5</v>
+        <v>225</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>148.5</v>
+        <v>225</v>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2261,19 +2261,19 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>员工029</t>
+          <t>财务员工05</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>人力资源部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>10.25</v>
+        <v>27</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2303,14 +2303,14 @@
         <v>0</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>168.75</v>
+        <v>225</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>168.75</v>
+        <v>225</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2322,19 +2322,19 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>员工030</t>
+          <t>财务员工06</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>人力资源部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -2349,10 +2349,10 @@
         <v>0</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9.77</v>
+        <v>27</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2364,14 +2364,14 @@
         <v>0</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>132.75</v>
+        <v>225</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>132.75</v>
+        <v>225</v>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>员工031</t>
+          <t>财务员工07</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2395,13 +2395,13 @@
         <v>3</v>
       </c>
       <c r="E32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>0</v>
@@ -2410,10 +2410,10 @@
         <v>0</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>17.87</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2425,14 +2425,14 @@
         <v>75</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>122.25</v>
+        <v>140.25</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>47.25</v>
+        <v>65.25</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>员工032</t>
+          <t>财务员工08</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2456,14 +2456,14 @@
         <v>3</v>
       </c>
       <c r="E33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H33" s="2" t="n">
         <v>0</v>
       </c>
@@ -2471,10 +2471,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>10.07</v>
+        <v>26.83</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2.07</v>
+        <v>2.83</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2483,17 +2483,17 @@
         <v>0</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>155.25</v>
+        <v>212.25</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>155.25</v>
+        <v>137.25</v>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2505,19 +2505,19 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>员工033</t>
+          <t>运营员工01</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>运营管理部</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
@@ -2532,10 +2532,10 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>10.03</v>
+        <v>26.95</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2547,14 +2547,14 @@
         <v>0</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>152.25</v>
+        <v>221.25</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>152.25</v>
+        <v>221.25</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2566,19 +2566,19 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>员工034</t>
+          <t>运营员工02</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>运营管理部</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>0</v>
@@ -2593,10 +2593,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>27</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2608,14 +2608,14 @@
         <v>0</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>122.25</v>
+        <v>225</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>122.25</v>
+        <v>225</v>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2627,19 +2627,19 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>员工035</t>
+          <t>运营员工03</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>运营管理部</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>26.98</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.72</v>
+        <v>2.98</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2669,14 +2669,14 @@
         <v>0</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>129</v>
+        <v>223.5</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>129</v>
+        <v>223.5</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2688,19 +2688,19 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>员工036</t>
+          <t>运营员工04</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>运营管理部</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>0</v>
@@ -2715,10 +2715,10 @@
         <v>0</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10.3</v>
+        <v>26.95</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2730,14 +2730,14 @@
         <v>0</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>172.5</v>
+        <v>221.25</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>172.5</v>
+        <v>221.25</v>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2749,23 +2749,23 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>员工037</t>
+          <t>运营员工05</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>运营管理部</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
@@ -2776,10 +2776,10 @@
         <v>0</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>26.92</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1.87</v>
+        <v>2.92</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2788,17 +2788,17 @@
         <v>0</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>140.25</v>
+        <v>219</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>140.25</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2810,19 +2810,19 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>员工038</t>
+          <t>运营员工06</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>运营管理部</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>9.85</v>
+        <v>27</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2852,14 +2852,14 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>138.75</v>
+        <v>225</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>138.75</v>
+        <v>225</v>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2871,23 +2871,23 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>员工039</t>
+          <t>运营员工07</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>运营管理部</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G40" s="2" t="n">
         <v>0</v>
       </c>
@@ -2898,10 +2898,10 @@
         <v>0</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>26.87</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1.78</v>
+        <v>2.87</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2910,17 +2910,17 @@
         <v>0</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>133.5</v>
+        <v>215.25</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>133.5</v>
+        <v>140.25</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2932,25 +2932,25 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>员工040</t>
+          <t>运营员工08</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>运营管理部</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>0</v>
@@ -2959,10 +2959,10 @@
         <v>0</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9.619999999999999</v>
+        <v>27</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2971,17 +2971,17 @@
         <v>0</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>121.5</v>
+        <v>225</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>46.5</v>
+        <v>225</v>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2993,22 +2993,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>员工041</t>
+          <t>门店员工01</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>运营管理部</t>
+          <t>门店运营部</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>0</v>
@@ -3020,10 +3020,10 @@
         <v>0</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10.15</v>
+        <v>26.67</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.15</v>
+        <v>2.67</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -3032,17 +3032,17 @@
         <v>0</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>161.25</v>
+        <v>200.25</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>161.25</v>
+        <v>50.25</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3054,25 +3054,25 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>员工042</t>
+          <t>门店员工02</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>运营管理部</t>
+          <t>门店运营部</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>0</v>
@@ -3081,10 +3081,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>9.5</v>
+        <v>26.98</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1.5</v>
+        <v>2.98</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -3093,17 +3093,17 @@
         <v>0</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>112.5</v>
+        <v>223.5</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>37.5</v>
+        <v>223.5</v>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3115,25 +3115,25 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>员工043</t>
+          <t>门店员工03</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>运营管理部</t>
+          <t>门店运营部</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>0</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>9.42</v>
+        <v>26.9</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1.42</v>
+        <v>2.9</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -3157,14 +3157,14 @@
         <v>75</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>106.5</v>
+        <v>217.5</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>31.5</v>
+        <v>142.5</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3176,23 +3176,23 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>员工044</t>
+          <t>门店员工04</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>运营管理部</t>
+          <t>门店运营部</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G45" s="2" t="n">
         <v>0</v>
       </c>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>10.15</v>
+        <v>17.67</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -3215,17 +3215,17 @@
         <v>0</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>161.25</v>
+        <v>125.25</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>161.25</v>
+        <v>50.25</v>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>员工045</t>
+          <t>门店员工05</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>运营管理部</t>
+          <t>门店运营部</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>0</v>
@@ -3264,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>10.12</v>
+        <v>26.66</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -3276,17 +3276,17 @@
         <v>0</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>159</v>
+        <v>199.5</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>159</v>
+        <v>49.5</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3298,19 +3298,19 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>员工046</t>
+          <t>门店员工06</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>运营管理部</t>
+          <t>门店运营部</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>0</v>
@@ -3325,10 +3325,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10.27</v>
+        <v>26.97</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2.27</v>
+        <v>2.97</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -3340,14 +3340,14 @@
         <v>0</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>170.25</v>
+        <v>222.75</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>170.25</v>
+        <v>222.75</v>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3359,19 +3359,19 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>员工047</t>
+          <t>门店员工07</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>运营管理部</t>
+          <t>门店运营部</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9.77</v>
+        <v>26.98</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1.77</v>
+        <v>2.98</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3401,14 +3401,14 @@
         <v>0</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>132.75</v>
+        <v>223.5</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>132.75</v>
+        <v>223.5</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3420,23 +3420,23 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>员工048</t>
+          <t>门店员工08</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>运营管理部</t>
+          <t>门店运营部</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G49" s="2" t="n">
         <v>0</v>
       </c>
@@ -3447,10 +3447,10 @@
         <v>0</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10.25</v>
+        <v>26.67</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3459,139 +3459,17 @@
         <v>0</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>168.75</v>
+        <v>200.25</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>168.75</v>
+        <v>125.25</v>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>EMP0049</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>员工049</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>运营管理部</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="2" t="n">
-        <v>167.25</v>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>167.25</v>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>EMP0050</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>员工050</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>运营管理部</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>132.75</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>132.75</v>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
